--- a/ui_runner/graded_slate/2026-04-10/graded_wcbb_2026-04-10.xlsx
+++ b/ui_runner/graded_slate/2026-04-10/graded_wcbb_2026-04-10.xlsx
@@ -673,7 +673,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CBB SLATE GRADE  |  2026-04-10  |  Generated 2026-04-11 17:53</t>
+          <t>CBB SLATE GRADE  |  2026-04-10  |  Generated 2026-04-12 00:06</t>
         </is>
       </c>
     </row>
